--- a/Personal MCP1 2026.xlsx
+++ b/Personal MCP1 2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\horario\plantilla horario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proyectos\02_pagina-horarios-mcp1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A642112-0362-4460-8E67-427597EB1D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC82521-6C24-4E79-B5FB-B8D5BE02E5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14610" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>JOSE DANIEL LUNA ENRIQUEZ</t>
   </si>
@@ -68,9 +68,6 @@
     <t>JOSE LEONARDO POSLIGUA MOLINA</t>
   </si>
   <si>
-    <t>BRAYAN STIK NIETO RAMIREZ</t>
-  </si>
-  <si>
     <t>JOSE GUSTAVO VALENZUELA TARAPUES</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>omar_wjr@hotmail.com</t>
   </si>
   <si>
-    <t>bstick04@gmail.com</t>
-  </si>
-  <si>
     <t>genechiscuet@gmail.com</t>
   </si>
   <si>
@@ -185,10 +179,46 @@
     <t>telefono de contacto</t>
   </si>
   <si>
-    <t>Pablo.julian.flores.armas@gmail.com</t>
-  </si>
-  <si>
-    <t>PABLO JULIÁN FLORES ARMAS</t>
+    <t>SANTIAGO DAVID MOROCHO CEBALLOS</t>
+  </si>
+  <si>
+    <t>santyldu600@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAEL JOSUE GUEVARA OBANDO </t>
+  </si>
+  <si>
+    <t>guevaramichael18g@gmail.com</t>
+  </si>
+  <si>
+    <t>cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asesor </t>
+  </si>
+  <si>
+    <t>sub jefe</t>
+  </si>
+  <si>
+    <t>jefe</t>
+  </si>
+  <si>
+    <t>tercer a bordo</t>
+  </si>
+  <si>
+    <t>operativo</t>
+  </si>
+  <si>
+    <t>Cajera</t>
+  </si>
+  <si>
+    <t>Asesora</t>
+  </si>
+  <si>
+    <t>asesor</t>
+  </si>
+  <si>
+    <t>asesora</t>
   </si>
 </sst>
 </file>
@@ -212,13 +242,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -227,7 +250,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -268,33 +297,33 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -576,520 +605,575 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5">
+        <v>1310559917</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="5">
+        <v>969057406</v>
+      </c>
+      <c r="H2" s="10">
+        <v>46050</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1729153807</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1729153807</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5">
+        <v>978764148</v>
+      </c>
+      <c r="H3" s="10">
+        <v>46231</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1150688420</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1150688420</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="5">
+        <v>991765242</v>
+      </c>
+      <c r="H4" s="10">
+        <v>46384</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1725290454</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1725290454</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="5">
+        <v>992777043</v>
+      </c>
+      <c r="H5" s="10">
+        <v>46264</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1755859038</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1755859038</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="5">
+        <v>998952209</v>
+      </c>
+      <c r="H6" s="10">
+        <v>46170</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1753456738</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1753456738</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5">
+        <v>991218319</v>
+      </c>
+      <c r="H7" s="10">
+        <v>46386</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8">
+        <v>931982136</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5">
+        <v>931982136</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="5">
+        <v>960012405</v>
+      </c>
+      <c r="H8" s="10">
+        <v>46041</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1727839142</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1727839142</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="5">
+        <v>939902571</v>
+      </c>
+      <c r="H9" s="10">
+        <v>46262</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1724158850</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1724158850</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="5">
+        <v>998456195</v>
+      </c>
+      <c r="H10" s="10">
+        <v>46357</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1714768486</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1714768486</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="5">
+        <v>981336694</v>
+      </c>
+      <c r="H11" s="10">
+        <v>46235</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1753544103</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1753544103</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5">
+        <v>99455935</v>
+      </c>
+      <c r="H12" s="10">
+        <v>46082</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1712323359</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1712323359</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="5">
+        <v>989272970</v>
+      </c>
+      <c r="H13" s="10">
+        <v>46047</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1729153807</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1753997376</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="5">
+        <v>987480148</v>
+      </c>
+      <c r="H14" s="10">
+        <v>46090</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="C15" s="12">
+        <v>1726862194</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1726862194</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="5">
+        <v>961145627</v>
+      </c>
+      <c r="H15" s="10">
+        <v>46054</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1729461796</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1729461796</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="5">
+        <v>983111606</v>
+      </c>
+      <c r="H16" s="10">
+        <v>46144</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="12">
+        <v>803422948</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="5">
+        <v>803422948</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="5">
+        <v>959591066</v>
+      </c>
+      <c r="H17" s="10">
+        <v>46136</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5">
+        <v>1752334951</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8">
-        <v>1310559917</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="2">
-        <v>969057406</v>
-      </c>
-      <c r="H2" s="12">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1729153807</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="8">
-        <v>1729153807</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2">
-        <v>978764148</v>
-      </c>
-      <c r="H3" s="12">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1150688420</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1150688420</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2">
-        <v>991765242</v>
-      </c>
-      <c r="H4" s="12">
-        <v>46384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1725290454</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="G18" s="5">
+        <v>963136397</v>
+      </c>
+      <c r="H18" s="10">
+        <v>46215</v>
+      </c>
+      <c r="I18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8">
-        <v>1725290454</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2">
-        <v>992777043</v>
-      </c>
-      <c r="H5" s="12">
-        <v>46264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1755859038</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1755859038</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2">
-        <v>998952209</v>
-      </c>
-      <c r="H6" s="12">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1753456738</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1753456738</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="2">
-        <v>991218319</v>
-      </c>
-      <c r="H7" s="12">
-        <v>46386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5">
-        <v>931982136</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="8">
-        <v>931982136</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2">
-        <v>960012405</v>
-      </c>
-      <c r="H8" s="12">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1727839142</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1727839142</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2">
-        <v>939902571</v>
-      </c>
-      <c r="H9" s="12">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1724158850</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1724158850</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="2">
-        <v>998456195</v>
-      </c>
-      <c r="H10" s="12">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1761707502</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1761707502</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2">
-        <v>962239999</v>
-      </c>
-      <c r="H11" s="12">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1714768486</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1714768486</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="2">
-        <v>981336694</v>
-      </c>
-      <c r="H12" s="12">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1753544103</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1753544103</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="2">
-        <v>99455935</v>
-      </c>
-      <c r="H13" s="12">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1712323359</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="13">
-        <v>1712323359</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="2">
-        <v>989272970</v>
-      </c>
-      <c r="H14" s="12">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1729153807</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="13">
-        <v>1753997376</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="2">
-        <v>987480148</v>
-      </c>
-      <c r="H15" s="12">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="10">
-        <v>1726862194</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1726862194</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="2">
-        <v>961145627</v>
-      </c>
-      <c r="H16" s="12">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1729461796</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="13">
-        <v>1729461796</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="2">
-        <v>983111606</v>
-      </c>
-      <c r="H17" s="12">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="10">
-        <v>803422948</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="13">
-        <v>803422948</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="2">
-        <v>959591066</v>
-      </c>
-      <c r="H18" s="12">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6">
+        <v>1750148155</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E19">
-        <v>1756162903</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19">
-        <v>995794306</v>
-      </c>
-      <c r="H19" s="15">
-        <v>36919</v>
+      <c r="G19" s="5">
+        <v>980670071</v>
+      </c>
+      <c r="H19" s="14">
+        <v>38248</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F17" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="F10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="F4" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="F5" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="F6" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="F9" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F2" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F19" r:id="rId17" xr:uid="{3A5423E2-0F83-48AB-ABD8-21094E9D8FB6}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F2" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>